--- a/check_in_forms/048_team_task_check_in_form--check_in_forms.xlsx
+++ b/check_in_forms/048_team_task_check_in_form--check_in_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,12 +1110,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1000,_'name':_'project',_'label':_'project'}</t>
+          <t>project</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1000, 'name': 'Project', 'label': 'Project'}</t>
+          <t>Project</t>
         </is>
       </c>
     </row>
@@ -1160,29 +1160,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1001,_'name':_'project',_'label':_'project',_'value':_1}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1001, 'name': 'Project', 'label': 'Project', 'value': 1}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>project_id_choices</t>
+          <t>task_id_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1002,_'name':_'project',_'label':_'project',_'value':_2}</t>
+          <t>task</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'name': 'Project', 'label': 'Project', 'value': 2}</t>
+          <t>Task</t>
         </is>
       </c>
     </row>
@@ -1194,743 +1194,454 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2000,_'name':_'task',_'label':_'task',_'value':_1}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2000, 'name': 'Task', 'label': 'Task', 'value': 1}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>task_id_choices</t>
+          <t>task_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2001,_'name':_'task',_'label':_'task',_'value':_2}</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2001, 'name': 'Task', 'label': 'Task', 'value': 2}</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>task_id_choices</t>
+          <t>task_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2002,_'name':_'task',_'label':_'task',_'value':_2}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2002, 'name': 'Task', 'label': 'Task', 'value': 2}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>task_status_choices</t>
+          <t>blockers_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5000,_'name':_'status',_'label':_'status'}</t>
+          <t>blockers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5000, 'name': 'Status', 'label': 'Status'}</t>
+          <t>Blockers</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>task_status_choices</t>
+          <t>blockers_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5001,_'name':_'status',_'label':_'status'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5001, 'name': 'Status', 'label': 'Status'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>task_status_choices</t>
+          <t>team_members_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5002,_'name':_'status',_'label':_'status'}</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5002, 'name': 'Status', 'label': 'Status'}</t>
+          <t>Team Members</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>task_status_choices</t>
+          <t>team_members_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5003,_'name':_'status',_'label':_'status'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5003, 'name': 'Status', 'label': 'Status'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>blockers_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6000,_'name':_'blockers',_'label':_'blockers'}</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6000, 'name': 'Blockers', 'label': 'Blockers'}</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>blockers_choices</t>
+          <t>location_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_6001,_'name':_'blockers',_'label':_'blockers'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 6001, 'name': 'Blockers', 'label': 'Blockers'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>blockers_choices</t>
+          <t>timezone_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_6002,_'name':_'blockers',_'label':_'blockers'}</t>
+          <t>timezone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 6002, 'name': 'Blockers', 'label': 'Blockers'}</t>
+          <t>Timezone</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>blockers_choices</t>
+          <t>timezone_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_6003,_'name':_'blockers',_'label':_'blockers'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 6003, 'name': 'Blockers', 'label': 'Blockers'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>team_members_choices</t>
+          <t>timezone_offset_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_7000,_'name':_'team_members',_'label':_'team_members',_'value':_1}</t>
+          <t>timezone_offset</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 7000, 'name': 'Team Members', 'label': 'Team Members', 'value': 1}</t>
+          <t>Timezone Offset</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>team_members_choices</t>
+          <t>timezone_offset_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_7001,_'name':_'team_members',_'label':_'team_members',_'value':_2}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 7001, 'name': 'Team Members', 'label': 'Team Members', 'value': 2}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>team_members_choices</t>
+          <t>user_timezone_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_7002,_'name':_'team_members',_'label':_'team_members',_'value':_2}</t>
+          <t>user_timezone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 7002, 'name': 'Team Members', 'label': 'Team Members', 'value': 2}</t>
+          <t>User Timezone</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>user_timezone_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_8000,_'name':_'location',_'label':_'location',_'value':_1}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 8000, 'name': 'Location', 'label': 'Location', 'value': 1}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>blocker_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_8001,_'name':_'location',_'label':_'location',_'value':_2}</t>
+          <t>blocker</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 8001, 'name': 'Location', 'label': 'Location', 'value': 2}</t>
+          <t>Blocker</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>blocker_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_8002,_'name':_'location',_'label':_'location',_'value':_2}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 8002, 'name': 'Location', 'label': 'Location', 'value': 2}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>team_lead_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_9000,_'name':_'timezone',_'label':_'timezone',_'value':_1}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 9000, 'name': 'Timezone', 'label': 'Timezone', 'value': 1}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>team_lead_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_9001,_'name':_'timezone',_'label':_'timezone',_'value':_2}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 9001, 'name': 'Timezone', 'label': 'Timezone', 'value': 2}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>team_lead_status_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_9002,_'name':_'timezone',_'label':_'timezone',_'value':_2}</t>
+          <t>team_lead_status</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 9002, 'name': 'Timezone', 'label': 'Timezone', 'value': 2}</t>
+          <t>Team Lead Status</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>timezone_offset_choices</t>
+          <t>team_lead_status_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_10000,_'name':_'timezone_offset',_'label':_'timezone_offset',_'value':_1}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 10000, 'name': 'Timezone Offset', 'label': 'Timezone Offset', 'value': 1}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>timezone_offset_choices</t>
+          <t>project_lead_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_10001,_'name':_'timezone_offset',_'label':_'timezone_offset',_'value':_2}</t>
+          <t>project_lead</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 10001, 'name': 'Timezone Offset', 'label': 'Timezone Offset', 'value': 2}</t>
+          <t>Project Lead</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>timezone_offset_choices</t>
+          <t>project_lead_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_10002,_'name':_'timezone_offset',_'label':_'timezone_offset',_'value':_2}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 10002, 'name': 'Timezone Offset', 'label': 'Timezone Offset', 'value': 2}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>user_timezone_choices</t>
+          <t>project_lead_status_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_11000,_'name':_'user_timezone',_'label':_'user_timezone',_'value':_1}</t>
+          <t>project_lead_status</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 11000, 'name': 'User Timezone', 'label': 'User Timezone', 'value': 1}</t>
+          <t>Project Lead Status</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>user_timezone_choices</t>
+          <t>project_lead_status_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_11001,_'name':_'user_timezone',_'label':_'user_timezone',_'value':_2}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 11001, 'name': 'User Timezone', 'label': 'User Timezone', 'value': 2}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>user_timezone_choices</t>
+          <t>blocker_lead_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_11002,_'name':_'user_timezone',_'label':_'user_timezone',_'value':_2}</t>
+          <t>blocker_lead</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 11002, 'name': 'User Timezone', 'label': 'User Timezone', 'value': 2}</t>
+          <t>Blocker Lead</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>blocker_choices</t>
+          <t>blocker_lead_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_12000,_'name':_'blocker',_'label':_'blocker',_'value':_1}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 12000, 'name': 'Blocker', 'label': 'Blocker', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>blocker_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'id':_12001,_'name':_'blocker',_'label':_'blocker',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'id': 12001, 'name': 'Blocker', 'label': 'Blocker', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>blocker_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'id':_12002,_'name':_'blocker',_'label':_'blocker',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'id': 12002, 'name': 'Blocker', 'label': 'Blocker', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>team_lead_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'id':_13000,_'name':_'team_lead',_'label':_'team_lead',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'id': 13000, 'name': 'Team Lead', 'label': 'Team Lead', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>team_lead_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'id':_13001,_'name':_'team_lead',_'label':_'team_lead',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'id': 13001, 'name': 'Team Lead', 'label': 'Team Lead', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>team_lead_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'id':_13002,_'name':_'team_lead',_'label':_'team_lead',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'id': 13002, 'name': 'Team Lead', 'label': 'Team Lead', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>team_lead_status_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'id':_14000,_'name':_'team_lead_status',_'label':_'team_lead_status',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'id': 14000, 'name': 'Team Lead Status', 'label': 'Team Lead Status', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>team_lead_status_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'id':_14001,_'name':_'team_lead_status',_'label':_'team_lead_status',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'id': 14001, 'name': 'Team Lead Status', 'label': 'Team Lead Status', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>team_lead_status_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'id':_14002,_'name':_'team_lead_status',_'label':_'team_lead_status',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'id': 14002, 'name': 'Team Lead Status', 'label': 'Team Lead Status', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>project_lead_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'id':_15000,_'name':_'project_lead',_'label':_'project_lead',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'id': 15000, 'name': 'Project Lead', 'label': 'Project Lead', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>project_lead_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'id':_15001,_'name':_'project_lead',_'label':_'project_lead',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'id': 15001, 'name': 'Project Lead', 'label': 'Project Lead', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>project_lead_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'id':_15002,_'name':_'project_lead',_'label':_'project_lead',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'id': 15002, 'name': 'Project Lead', 'label': 'Project Lead', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>project_lead_status_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'id':_16000,_'name':_'project_lead_status',_'label':_'project_lead_status',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'id': 16000, 'name': 'Project Lead Status', 'label': 'Project Lead Status', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>project_lead_status_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'id':_16001,_'name':_'project_lead_status',_'label':_'project_lead_status',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'id': 16001, 'name': 'Project Lead Status', 'label': 'Project Lead Status', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>project_lead_status_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'id':_16002,_'name':_'project_lead_status',_'label':_'project_lead_status',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'id': 16002, 'name': 'Project Lead Status', 'label': 'Project Lead Status', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>blocker_lead_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'id':_17000,_'name':_'blocker_lead',_'label':_'blocker_lead',_'value':_1}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'id': 17000, 'name': 'Blocker Lead', 'label': 'Blocker Lead', 'value': 1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>blocker_lead_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'id':_17001,_'name':_'blocker_lead',_'label':_'blocker_lead',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'id': 17001, 'name': 'Blocker Lead', 'label': 'Blocker Lead', 'value': 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>blocker_lead_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'id':_17002,_'name':_'blocker_lead',_'label':_'blocker_lead',_'value':_2}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'id': 17002, 'name': 'Blocker Lead', 'label': 'Blocker Lead', 'value': 2}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
